--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/87.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/87.xlsx
@@ -426,13 +426,13 @@
         <v>-13.53990455810236</v>
       </c>
       <c r="E2">
-        <v>-9.248540770364833</v>
+        <v>-12.15110694184722</v>
       </c>
       <c r="F2">
-        <v>5.822881369180124</v>
+        <v>4.467746977398305</v>
       </c>
       <c r="G2">
-        <v>-16.80751174227212</v>
+        <v>-15.91220449608608</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.52629621352441</v>
       </c>
       <c r="E3">
-        <v>-10.77043408707063</v>
+        <v>-11.1643252847318</v>
       </c>
       <c r="F3">
-        <v>6.123099748452233</v>
+        <v>4.216237057261452</v>
       </c>
       <c r="G3">
-        <v>-15.63291032166547</v>
+        <v>-16.03095376457974</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.23807875336145</v>
       </c>
       <c r="E4">
-        <v>-11.1529859858166</v>
+        <v>-11.69994413341104</v>
       </c>
       <c r="F4">
-        <v>5.729532991406376</v>
+        <v>4.520961079862986</v>
       </c>
       <c r="G4">
-        <v>-15.24922968057332</v>
+        <v>-14.52789491302152</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.798044006134324</v>
       </c>
       <c r="E5">
-        <v>-10.3213090919379</v>
+        <v>-12.11704376036152</v>
       </c>
       <c r="F5">
-        <v>5.805690241468029</v>
+        <v>4.993112908138865</v>
       </c>
       <c r="G5">
-        <v>-14.29177687352409</v>
+        <v>-15.01072970356038</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.192615795832557</v>
       </c>
       <c r="E6">
-        <v>-11.95838414502878</v>
+        <v>-15.04405463453731</v>
       </c>
       <c r="F6">
-        <v>5.879112431413717</v>
+        <v>4.358659730236921</v>
       </c>
       <c r="G6">
-        <v>-13.29658550259992</v>
+        <v>-12.32478148063795</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.486146376891678</v>
       </c>
       <c r="E7">
-        <v>-13.30803695285283</v>
+        <v>-14.19778246893189</v>
       </c>
       <c r="F7">
-        <v>6.037388000602736</v>
+        <v>5.002930301108673</v>
       </c>
       <c r="G7">
-        <v>-12.43301314595334</v>
+        <v>-13.86158472287795</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.68735058266603</v>
       </c>
       <c r="E8">
-        <v>-14.64035476217552</v>
+        <v>-17.48144237052977</v>
       </c>
       <c r="F8">
-        <v>5.854685351373979</v>
+        <v>4.977606843520797</v>
       </c>
       <c r="G8">
-        <v>-10.56444523776804</v>
+        <v>-11.23951513140853</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.850040591069241</v>
       </c>
       <c r="E9">
-        <v>-14.51644665637765</v>
+        <v>-16.55344030603392</v>
       </c>
       <c r="F9">
-        <v>5.865910658902614</v>
+        <v>5.222490538107452</v>
       </c>
       <c r="G9">
-        <v>-9.993098046418465</v>
+        <v>-9.770023556345754</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.9958863450507245</v>
       </c>
       <c r="E10">
-        <v>-16.37986389731991</v>
+        <v>-16.40242022635212</v>
       </c>
       <c r="F10">
-        <v>5.666956019569618</v>
+        <v>4.830893911220402</v>
       </c>
       <c r="G10">
-        <v>-8.917538216710188</v>
+        <v>-8.485313391102942</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.835978366410575</v>
       </c>
       <c r="E11">
-        <v>-17.04337138044977</v>
+        <v>-18.47228154035606</v>
       </c>
       <c r="F11">
-        <v>6.04256038412256</v>
+        <v>5.051700524774631</v>
       </c>
       <c r="G11">
-        <v>-6.974956441903405</v>
+        <v>-7.777535307534459</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.606081418421875</v>
       </c>
       <c r="E12">
-        <v>-17.89830198835785</v>
+        <v>-19.3503254795993</v>
       </c>
       <c r="F12">
-        <v>5.841521587804847</v>
+        <v>5.017131392052419</v>
       </c>
       <c r="G12">
-        <v>-7.162247245242133</v>
+        <v>-7.497972978925164</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>4.293376655597667</v>
       </c>
       <c r="E13">
-        <v>-18.80604366014339</v>
+        <v>-19.1720304009693</v>
       </c>
       <c r="F13">
-        <v>6.205173723813967</v>
+        <v>5.265429556592762</v>
       </c>
       <c r="G13">
-        <v>-5.980488425179576</v>
+        <v>-6.516796802541508</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.849947756791613</v>
       </c>
       <c r="E14">
-        <v>-19.20909596072208</v>
+        <v>-20.39732225559471</v>
       </c>
       <c r="F14">
-        <v>5.85831045421442</v>
+        <v>4.881184492565182</v>
       </c>
       <c r="G14">
-        <v>-5.404344253343594</v>
+        <v>-6.790482912818597</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>7.267890889148476</v>
       </c>
       <c r="E15">
-        <v>-20.97972024077318</v>
+        <v>-22.0483902933693</v>
       </c>
       <c r="F15">
-        <v>6.167129940313282</v>
+        <v>5.405150427276492</v>
       </c>
       <c r="G15">
-        <v>-3.303720345037544</v>
+        <v>-4.673101022992756</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>8.51259599303461</v>
       </c>
       <c r="E16">
-        <v>-21.00977119428808</v>
+        <v>-22.79191591221469</v>
       </c>
       <c r="F16">
-        <v>6.310035643592959</v>
+        <v>5.524512758417248</v>
       </c>
       <c r="G16">
-        <v>-3.402113069010223</v>
+        <v>-3.22093022219145</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>9.583009578638316</v>
       </c>
       <c r="E17">
-        <v>-22.7644144895661</v>
+        <v>-25.08598197433839</v>
       </c>
       <c r="F17">
-        <v>5.950013361542026</v>
+        <v>5.425816205767061</v>
       </c>
       <c r="G17">
-        <v>-3.397455131436468</v>
+        <v>-3.473749963934512</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>10.46446334680094</v>
       </c>
       <c r="E18">
-        <v>-23.46708421591429</v>
+        <v>-24.5480264330712</v>
       </c>
       <c r="F18">
-        <v>5.969730500189247</v>
+        <v>5.423500827718689</v>
       </c>
       <c r="G18">
-        <v>-2.035082878387893</v>
+        <v>-3.424346692851968</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>11.15369110526163</v>
       </c>
       <c r="E19">
-        <v>-24.87427128600579</v>
+        <v>-24.85909636960609</v>
       </c>
       <c r="F19">
-        <v>6.035033029906477</v>
+        <v>5.836920922120495</v>
       </c>
       <c r="G19">
-        <v>-2.233195855094499</v>
+        <v>-2.925315058262229</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>11.65171428511378</v>
       </c>
       <c r="E20">
-        <v>-25.56500848334377</v>
+        <v>-27.55809857749568</v>
       </c>
       <c r="F20">
-        <v>6.357228496167139</v>
+        <v>6.062846073193424</v>
       </c>
       <c r="G20">
-        <v>-2.021844006776347</v>
+        <v>-3.676679784400757</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>11.95588302273025</v>
       </c>
       <c r="E21">
-        <v>-26.24756725662389</v>
+        <v>-27.59377842420211</v>
       </c>
       <c r="F21">
-        <v>6.264076497926907</v>
+        <v>5.381355245897014</v>
       </c>
       <c r="G21">
-        <v>-1.390162122973551</v>
+        <v>-1.560979651708866</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>12.07658885410273</v>
       </c>
       <c r="E22">
-        <v>-26.43180369315195</v>
+        <v>-27.76298032702471</v>
       </c>
       <c r="F22">
-        <v>6.400501676600608</v>
+        <v>5.401403379080562</v>
       </c>
       <c r="G22">
-        <v>-1.177204660068854</v>
+        <v>-1.373880860011416</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>12.01973845816182</v>
       </c>
       <c r="E23">
-        <v>-26.0828530715429</v>
+        <v>-27.68813823709994</v>
       </c>
       <c r="F23">
-        <v>5.988723885233112</v>
+        <v>5.507453078296134</v>
       </c>
       <c r="G23">
-        <v>-1.38939738695398</v>
+        <v>-1.978965820951707</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>11.80403063095668</v>
       </c>
       <c r="E24">
-        <v>-26.37596760863738</v>
+        <v>-28.11440349544195</v>
       </c>
       <c r="F24">
-        <v>6.163468412236785</v>
+        <v>5.641885954928211</v>
       </c>
       <c r="G24">
-        <v>-0.4945006484148104</v>
+        <v>-1.542447217780026</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>11.44611242812438</v>
       </c>
       <c r="E25">
-        <v>-27.30903250707381</v>
+        <v>-29.2996953391576</v>
       </c>
       <c r="F25">
-        <v>5.879437091126382</v>
+        <v>5.220666108892866</v>
       </c>
       <c r="G25">
-        <v>-0.1488465886595058</v>
+        <v>-1.224022395085227</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>10.97194812046492</v>
       </c>
       <c r="E26">
-        <v>-28.076645079166</v>
+        <v>-30.98840858135796</v>
       </c>
       <c r="F26">
-        <v>5.7333101300147</v>
+        <v>5.045493981292024</v>
       </c>
       <c r="G26">
-        <v>-0.5493861829103874</v>
+        <v>-0.7223290818819142</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>10.405349198332</v>
       </c>
       <c r="E27">
-        <v>-28.00763566376311</v>
+        <v>-27.23477911877004</v>
       </c>
       <c r="F27">
-        <v>5.727151097709556</v>
+        <v>5.422658296171675</v>
       </c>
       <c r="G27">
-        <v>0.2255728012865262</v>
+        <v>-0.3875402325864976</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>9.779249763351554</v>
       </c>
       <c r="E28">
-        <v>-27.69940508043102</v>
+        <v>-28.16799798532273</v>
       </c>
       <c r="F28">
-        <v>5.787040520607814</v>
+        <v>4.835155663838849</v>
       </c>
       <c r="G28">
-        <v>-0.2965234040753149</v>
+        <v>-0.7194323545350519</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>9.116684052208635</v>
       </c>
       <c r="E29">
-        <v>-27.20792073943054</v>
+        <v>-29.25420228927655</v>
       </c>
       <c r="F29">
-        <v>5.740517575635865</v>
+        <v>4.996856788922964</v>
       </c>
       <c r="G29">
-        <v>0.5098096201972718</v>
+        <v>0.1863064206452307</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.451272188315096</v>
       </c>
       <c r="E30">
-        <v>-26.96239593568267</v>
+        <v>-29.27502421276382</v>
       </c>
       <c r="F30">
-        <v>5.875303618687085</v>
+        <v>4.242759380227316</v>
       </c>
       <c r="G30">
-        <v>0.3049067145896209</v>
+        <v>-0.0152726972409919</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>7.80176672893758</v>
       </c>
       <c r="E31">
-        <v>-27.55570301474562</v>
+        <v>-29.12158592796192</v>
       </c>
       <c r="F31">
-        <v>5.399088001032189</v>
+        <v>4.849323496958371</v>
       </c>
       <c r="G31">
-        <v>-0.0997909248585853</v>
+        <v>-0.7977068932655799</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>7.188769717813312</v>
       </c>
       <c r="E32">
-        <v>-27.06493870111236</v>
+        <v>-27.46703096520143</v>
       </c>
       <c r="F32">
-        <v>5.563924863828873</v>
+        <v>4.922096367478729</v>
       </c>
       <c r="G32">
-        <v>-0.7495715611245768</v>
+        <v>0.8602076917103521</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.623667925686522</v>
       </c>
       <c r="E33">
-        <v>-26.04887593106335</v>
+        <v>-28.25590019428562</v>
       </c>
       <c r="F33">
-        <v>5.307716088240911</v>
+        <v>5.147140978062675</v>
       </c>
       <c r="G33">
-        <v>-0.9726857777437584</v>
+        <v>-0.1043363038840046</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.110044331843737</v>
       </c>
       <c r="E34">
-        <v>-26.94751537009347</v>
+        <v>-28.36120080038598</v>
       </c>
       <c r="F34">
-        <v>6.045620103951189</v>
+        <v>4.776875286150678</v>
       </c>
       <c r="G34">
-        <v>0.1221314953664587</v>
+        <v>-0.07131361212977455</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.651628149323185</v>
       </c>
       <c r="E35">
-        <v>-24.79324782906055</v>
+        <v>-26.61896099541496</v>
       </c>
       <c r="F35">
-        <v>5.935516117592093</v>
+        <v>5.011211499340506</v>
       </c>
       <c r="G35">
-        <v>-0.3480421137574531</v>
+        <v>-1.59989180397746</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.235889176077079</v>
       </c>
       <c r="E36">
-        <v>-24.07550281274084</v>
+        <v>-27.96114182112635</v>
       </c>
       <c r="F36">
-        <v>6.507545943131075</v>
+        <v>5.139578782316451</v>
       </c>
       <c r="G36">
-        <v>-0.7277616871118582</v>
+        <v>-1.510957308610479</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.862681899637241</v>
       </c>
       <c r="E37">
-        <v>-24.33257069673426</v>
+        <v>-25.9368505410616</v>
       </c>
       <c r="F37">
-        <v>6.123828253173336</v>
+        <v>5.04528334840527</v>
       </c>
       <c r="G37">
-        <v>-1.165197311397917</v>
+        <v>-2.248176073659701</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.515834493171199</v>
       </c>
       <c r="E38">
-        <v>-24.53272471939928</v>
+        <v>-25.24809681533898</v>
       </c>
       <c r="F38">
-        <v>6.60452417486301</v>
+        <v>5.268688823366737</v>
       </c>
       <c r="G38">
-        <v>-1.021062779709128</v>
+        <v>-1.568070840253985</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.192337724224303</v>
       </c>
       <c r="E39">
-        <v>-24.10791762968774</v>
+        <v>-25.32859496929933</v>
       </c>
       <c r="F39">
-        <v>6.419833974710377</v>
+        <v>5.553961769914844</v>
       </c>
       <c r="G39">
-        <v>-1.563796925962786</v>
+        <v>-1.608628333655596</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.882815076263818</v>
       </c>
       <c r="E40">
-        <v>-22.98312619871456</v>
+        <v>-23.6821686173826</v>
       </c>
       <c r="F40">
-        <v>6.513994793618744</v>
+        <v>5.942739400272412</v>
       </c>
       <c r="G40">
-        <v>-1.224548771825971</v>
+        <v>-1.283413582059752</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.583354151684926</v>
       </c>
       <c r="E41">
-        <v>-23.19877213095982</v>
+        <v>-23.90037766591621</v>
       </c>
       <c r="F41">
-        <v>6.649639205276134</v>
+        <v>5.734095648148758</v>
       </c>
       <c r="G41">
-        <v>-1.619182352834793</v>
+        <v>-2.970381514688328</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.291474350028667</v>
       </c>
       <c r="E42">
-        <v>-21.3034427336855</v>
+        <v>-22.32313733988867</v>
       </c>
       <c r="F42">
-        <v>6.67139615714244</v>
+        <v>6.269066755266457</v>
       </c>
       <c r="G42">
-        <v>-1.723229488588547</v>
+        <v>-2.767819164776942</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.001188370786404</v>
       </c>
       <c r="E43">
-        <v>-21.70078915701453</v>
+        <v>-21.30081621876105</v>
       </c>
       <c r="F43">
-        <v>6.757061977520391</v>
+        <v>5.878261981337126</v>
       </c>
       <c r="G43">
-        <v>-3.422049174247714</v>
+        <v>-2.449149361712237</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.7137885990524</v>
       </c>
       <c r="E44">
-        <v>-20.22857320017288</v>
+        <v>-21.19772097950243</v>
       </c>
       <c r="F44">
-        <v>6.68161264400294</v>
+        <v>6.236779742768393</v>
       </c>
       <c r="G44">
-        <v>-3.192287382185675</v>
+        <v>-3.371497143863043</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.420271811862897</v>
       </c>
       <c r="E45">
-        <v>-19.7216195919622</v>
+        <v>-20.87652537508639</v>
       </c>
       <c r="F45">
-        <v>6.670591634537397</v>
+        <v>6.052442709034903</v>
       </c>
       <c r="G45">
-        <v>-4.046067145127097</v>
+        <v>-3.016176291133066</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.122011335910348</v>
       </c>
       <c r="E46">
-        <v>-18.64963922486647</v>
+        <v>-19.87280722518228</v>
       </c>
       <c r="F46">
-        <v>7.136405471739686</v>
+        <v>6.030007931036788</v>
       </c>
       <c r="G46">
-        <v>-3.030368599859922</v>
+        <v>-3.633609586934839</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.810884969627655</v>
       </c>
       <c r="E47">
-        <v>-19.02379986127623</v>
+        <v>-18.6903320922994</v>
       </c>
       <c r="F47">
-        <v>7.117575208405111</v>
+        <v>6.200618985601164</v>
       </c>
       <c r="G47">
-        <v>-3.54766451418982</v>
+        <v>-3.996696979499946</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.487147780712398</v>
       </c>
       <c r="E48">
-        <v>-18.06414376346676</v>
+        <v>-17.86615887985141</v>
       </c>
       <c r="F48">
-        <v>7.285112289787619</v>
+        <v>6.610892256348992</v>
       </c>
       <c r="G48">
-        <v>-4.765183847167584</v>
+        <v>-5.378128043218105</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.146952491635499</v>
       </c>
       <c r="E49">
-        <v>-16.88363851677721</v>
+        <v>-18.6042548583616</v>
       </c>
       <c r="F49">
-        <v>7.675799869479207</v>
+        <v>6.430059963806369</v>
       </c>
       <c r="G49">
-        <v>-5.039740630921501</v>
+        <v>-4.624624704661208</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.7893506254452884</v>
       </c>
       <c r="E50">
-        <v>-16.89481026215413</v>
+        <v>-18.0944573684741</v>
       </c>
       <c r="F50">
-        <v>7.493203328546786</v>
+        <v>6.106171515922101</v>
       </c>
       <c r="G50">
-        <v>-5.26400360684281</v>
+        <v>-5.034678806791955</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.4167255602567508</v>
       </c>
       <c r="E51">
-        <v>-15.78869878646259</v>
+        <v>-17.65138241461562</v>
       </c>
       <c r="F51">
-        <v>7.892105590821759</v>
+        <v>6.647467944466066</v>
       </c>
       <c r="G51">
-        <v>-6.129909898094581</v>
+        <v>-5.773953420621065</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.02580177307786443</v>
       </c>
       <c r="E52">
-        <v>-15.37175765610238</v>
+        <v>-15.76234759621196</v>
       </c>
       <c r="F52">
-        <v>7.696567005148365</v>
+        <v>6.818725151043942</v>
       </c>
       <c r="G52">
-        <v>-5.920435129097197</v>
+        <v>-5.273733300182728</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.3770229980463828</v>
       </c>
       <c r="E53">
-        <v>-15.32970624646715</v>
+        <v>-15.94124043341097</v>
       </c>
       <c r="F53">
-        <v>7.566853572144297</v>
+        <v>6.857269385613907</v>
       </c>
       <c r="G53">
-        <v>-5.850731592767842</v>
+        <v>-5.581339260055189</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.7942715443180138</v>
       </c>
       <c r="E54">
-        <v>-14.32131018291312</v>
+        <v>-15.24357919931527</v>
       </c>
       <c r="F54">
-        <v>7.681098949472268</v>
+        <v>6.889383774167188</v>
       </c>
       <c r="G54">
-        <v>-7.336216413330834</v>
+        <v>-7.006443040527413</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.216678855511815</v>
       </c>
       <c r="E55">
-        <v>-14.96451198859258</v>
+        <v>-14.98322817166628</v>
       </c>
       <c r="F55">
-        <v>7.668524324503679</v>
+        <v>6.74013691240209</v>
       </c>
       <c r="G55">
-        <v>-6.213603799872896</v>
+        <v>-6.326182211481352</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.64428410530531</v>
       </c>
       <c r="E56">
-        <v>-13.49755811854785</v>
+        <v>-14.53130005112281</v>
       </c>
       <c r="F56">
-        <v>7.840155285677598</v>
+        <v>7.219157273233228</v>
       </c>
       <c r="G56">
-        <v>-7.575019305260622</v>
+        <v>-6.651840576179459</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.070202985699526</v>
       </c>
       <c r="E57">
-        <v>-12.83295927318214</v>
+        <v>-14.0568608862872</v>
       </c>
       <c r="F57">
-        <v>8.315867284851384</v>
+        <v>7.064573322533099</v>
       </c>
       <c r="G57">
-        <v>-7.502892449596521</v>
+        <v>-6.513949733377736</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.489967989248726</v>
       </c>
       <c r="E58">
-        <v>-12.67622425930267</v>
+        <v>-14.52012830574588</v>
       </c>
       <c r="F58">
-        <v>8.112486187484734</v>
+        <v>6.724914331142886</v>
       </c>
       <c r="G58">
-        <v>-7.840932254611501</v>
+        <v>-6.753414734415378</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.899479740211248</v>
       </c>
       <c r="E59">
-        <v>-12.12112391544243</v>
+        <v>-11.96891737557062</v>
       </c>
       <c r="F59">
-        <v>8.253500945901379</v>
+        <v>6.76055563276985</v>
       </c>
       <c r="G59">
-        <v>-8.460924602115131</v>
+        <v>-7.914691209226463</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.289666016899956</v>
       </c>
       <c r="E60">
-        <v>-12.53191537810024</v>
+        <v>-14.36047695460546</v>
       </c>
       <c r="F60">
-        <v>8.242012743190781</v>
+        <v>7.006463985083795</v>
       </c>
       <c r="G60">
-        <v>-8.735881961879299</v>
+        <v>-7.385689205869703</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.657505882570607</v>
       </c>
       <c r="E61">
-        <v>-11.88334733072169</v>
+        <v>-11.98928645165713</v>
       </c>
       <c r="F61">
-        <v>7.836305296597165</v>
+        <v>6.544709186142777</v>
       </c>
       <c r="G61">
-        <v>-8.883002605644512</v>
+        <v>-7.686637658662689</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.991872965923478</v>
       </c>
       <c r="E62">
-        <v>-12.14392478207105</v>
+        <v>-13.34447305471855</v>
       </c>
       <c r="F62">
-        <v>8.608038854367146</v>
+        <v>7.048265902721819</v>
       </c>
       <c r="G62">
-        <v>-9.030841637791744</v>
+        <v>-8.296897002280861</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.290306157005396</v>
       </c>
       <c r="E63">
-        <v>-11.66163324330615</v>
+        <v>-10.88815176890002</v>
       </c>
       <c r="F63">
-        <v>8.158643296390217</v>
+        <v>7.306324446819016</v>
       </c>
       <c r="G63">
-        <v>-9.61037580825994</v>
+        <v>-8.501339742058553</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.544117780313718</v>
       </c>
       <c r="E64">
-        <v>-10.11593373874203</v>
+        <v>-10.89397991494789</v>
       </c>
       <c r="F64">
-        <v>8.116011516852502</v>
+        <v>7.524560705672487</v>
       </c>
       <c r="G64">
-        <v>-9.615450874571643</v>
+        <v>-9.371440494508581</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.751025836104803</v>
       </c>
       <c r="E65">
-        <v>-10.52319299167385</v>
+        <v>-11.12021794789709</v>
       </c>
       <c r="F65">
-        <v>8.222238591130603</v>
+        <v>7.007753121698963</v>
       </c>
       <c r="G65">
-        <v>-10.25075780573994</v>
+        <v>-8.364994924023669</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.907423766020123</v>
       </c>
       <c r="E66">
-        <v>-10.38409185558024</v>
+        <v>-9.625880395527975</v>
       </c>
       <c r="F66">
-        <v>8.149907574560654</v>
+        <v>6.884567724478337</v>
       </c>
       <c r="G66">
-        <v>-9.15196125689152</v>
+        <v>-9.064446985560886</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.012752574903891</v>
       </c>
       <c r="E67">
-        <v>-9.577366853483802</v>
+        <v>-10.77736718077637</v>
       </c>
       <c r="F67">
-        <v>7.66804129419947</v>
+        <v>7.029484734270623</v>
       </c>
       <c r="G67">
-        <v>-10.78840695404528</v>
+        <v>-8.738755515407387</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.068507794010076</v>
       </c>
       <c r="E68">
-        <v>-8.927050815138292</v>
+        <v>-10.08077013807247</v>
       </c>
       <c r="F68">
-        <v>8.074486747749681</v>
+        <v>6.555823634257331</v>
       </c>
       <c r="G68">
-        <v>-10.12731087312606</v>
+        <v>-9.950438356599417</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.076796084985699</v>
       </c>
       <c r="E69">
-        <v>-8.996146271547326</v>
+        <v>-10.39566210666984</v>
       </c>
       <c r="F69">
-        <v>7.855563160528908</v>
+        <v>6.62130037162526</v>
       </c>
       <c r="G69">
-        <v>-9.73261108120645</v>
+        <v>-9.535146971425542</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.042767950284731</v>
       </c>
       <c r="E70">
-        <v>-9.306007105522172</v>
+        <v>-8.359809632463495</v>
       </c>
       <c r="F70">
-        <v>7.825507589665698</v>
+        <v>6.800586967194413</v>
       </c>
       <c r="G70">
-        <v>-10.87994022766059</v>
+        <v>-9.094649092515658</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.969386104398196</v>
       </c>
       <c r="E71">
-        <v>-9.854006802138377</v>
+        <v>-9.376012785206747</v>
       </c>
       <c r="F71">
-        <v>7.587665051579087</v>
+        <v>6.704227964475415</v>
       </c>
       <c r="G71">
-        <v>-10.5865530608793</v>
+        <v>-10.34502227942515</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.863792213362989</v>
       </c>
       <c r="E72">
-        <v>-10.31288160180962</v>
+        <v>-9.981356548182083</v>
       </c>
       <c r="F72">
-        <v>7.560645444955775</v>
+        <v>6.543323443466767</v>
       </c>
       <c r="G72">
-        <v>-11.14210232891547</v>
+        <v>-10.54709135805118</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.730636815822482</v>
       </c>
       <c r="E73">
-        <v>-8.783244594550712</v>
+        <v>-8.765194097156138</v>
       </c>
       <c r="F73">
-        <v>7.52298650199254</v>
+        <v>6.274769680267954</v>
       </c>
       <c r="G73">
-        <v>-11.31389977913041</v>
+        <v>-9.388168681118518</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.577623600181431</v>
       </c>
       <c r="E74">
-        <v>-9.8602198684769</v>
+        <v>-9.144693804420937</v>
       </c>
       <c r="F74">
-        <v>7.528822458290934</v>
+        <v>6.369194978064201</v>
       </c>
       <c r="G74">
-        <v>-10.8521481978584</v>
+        <v>-9.478500226703073</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.407662838283652</v>
       </c>
       <c r="E75">
-        <v>-9.892784125066058</v>
+        <v>-10.67362436973465</v>
       </c>
       <c r="F75">
-        <v>7.108663695218934</v>
+        <v>6.098848459769109</v>
       </c>
       <c r="G75">
-        <v>-10.29278187081545</v>
+        <v>-10.59428649525903</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.228209255431743</v>
       </c>
       <c r="E76">
-        <v>-10.422918991722</v>
+        <v>-9.490374867796454</v>
       </c>
       <c r="F76">
-        <v>7.289850737886614</v>
+        <v>6.332677887065998</v>
       </c>
       <c r="G76">
-        <v>-10.10893403483756</v>
+        <v>-9.673703233880659</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.040739247721291</v>
       </c>
       <c r="E77">
-        <v>-10.60423003404111</v>
+        <v>-11.61175210211166</v>
       </c>
       <c r="F77">
-        <v>7.28345573340007</v>
+        <v>5.941877864254414</v>
       </c>
       <c r="G77">
-        <v>-10.56000910674542</v>
+        <v>-9.416996911674493</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.849174707321867</v>
       </c>
       <c r="E78">
-        <v>-10.90258854403647</v>
+        <v>-10.82468520568252</v>
       </c>
       <c r="F78">
-        <v>7.444881293654897</v>
+        <v>6.123780741995873</v>
       </c>
       <c r="G78">
-        <v>-10.29983995390518</v>
+        <v>-10.11216512728389</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.654013155606401</v>
       </c>
       <c r="E79">
-        <v>-11.24191615837923</v>
+        <v>-11.70764253922408</v>
       </c>
       <c r="F79">
-        <v>7.138575148843838</v>
+        <v>5.892432981868478</v>
       </c>
       <c r="G79">
-        <v>-10.28999439147138</v>
+        <v>-9.351590463455112</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.455117018487658</v>
       </c>
       <c r="E80">
-        <v>-12.26154736594628</v>
+        <v>-11.91267825686937</v>
       </c>
       <c r="F80">
-        <v>7.166423033660926</v>
+        <v>6.08283244184627</v>
       </c>
       <c r="G80">
-        <v>-10.53411401953724</v>
+        <v>-9.003122439991426</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.252441260848772</v>
       </c>
       <c r="E81">
-        <v>-12.37781140761921</v>
+        <v>-11.81307899954466</v>
       </c>
       <c r="F81">
-        <v>7.4865169221718</v>
+        <v>5.709883952113519</v>
       </c>
       <c r="G81">
-        <v>-11.03470823162152</v>
+        <v>-9.520348832865</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.041657755526386</v>
       </c>
       <c r="E82">
-        <v>-12.92026825205003</v>
+        <v>-13.20479227395196</v>
       </c>
       <c r="F82">
-        <v>7.090845419964324</v>
+        <v>6.000145572295262</v>
       </c>
       <c r="G82">
-        <v>-9.42196604052894</v>
+        <v>-8.87160108680726</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.823361630817571</v>
       </c>
       <c r="E83">
-        <v>-14.5902154979626</v>
+        <v>-12.97205135232774</v>
       </c>
       <c r="F83">
-        <v>7.192506670088213</v>
+        <v>6.304318465238223</v>
       </c>
       <c r="G83">
-        <v>-10.93374652431036</v>
+        <v>-8.410481819733256</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.591694940449159</v>
       </c>
       <c r="E84">
-        <v>-15.99904640411888</v>
+        <v>-14.29500427740257</v>
       </c>
       <c r="F84">
-        <v>7.298858857133634</v>
+        <v>5.908379316731038</v>
       </c>
       <c r="G84">
-        <v>-9.944711112816478</v>
+        <v>-8.360078763897851</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.348392855096331</v>
       </c>
       <c r="E85">
-        <v>-17.06535712175701</v>
+        <v>-16.56091681662058</v>
       </c>
       <c r="F85">
-        <v>7.094468939098849</v>
+        <v>6.219791329413474</v>
       </c>
       <c r="G85">
-        <v>-9.13547474010595</v>
+        <v>-7.900098324489356</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.090234719332969</v>
       </c>
       <c r="E86">
-        <v>-17.80633773821008</v>
+        <v>-17.05168113025384</v>
       </c>
       <c r="F86">
-        <v>7.582681129063199</v>
+        <v>5.845738996657661</v>
       </c>
       <c r="G86">
-        <v>-9.547935608843746</v>
+        <v>-7.604837388932838</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.81967732848972</v>
       </c>
       <c r="E87">
-        <v>-18.47927803269792</v>
+        <v>-18.11896094132961</v>
       </c>
       <c r="F87">
-        <v>7.204992607525538</v>
+        <v>6.207150188796436</v>
       </c>
       <c r="G87">
-        <v>-9.101518474509644</v>
+        <v>-8.148399171571313</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.538805027660682</v>
       </c>
       <c r="E88">
-        <v>-19.82803420266844</v>
+        <v>-18.62365484101046</v>
       </c>
       <c r="F88">
-        <v>7.037898963799353</v>
+        <v>5.41876713073744</v>
       </c>
       <c r="G88">
-        <v>-8.219638801030889</v>
+        <v>-6.449354368815476</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.251245760273717</v>
       </c>
       <c r="E89">
-        <v>-20.56828573480629</v>
+        <v>-22.38553518324036</v>
       </c>
       <c r="F89">
-        <v>7.282893517800089</v>
+        <v>5.905750364911409</v>
       </c>
       <c r="G89">
-        <v>-8.375045740280896</v>
+        <v>-6.694410881268947</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.9648256029433809</v>
       </c>
       <c r="E90">
-        <v>-22.77328124167312</v>
+        <v>-22.96178350071641</v>
       </c>
       <c r="F90">
-        <v>6.817553208666516</v>
+        <v>5.835829748744757</v>
       </c>
       <c r="G90">
-        <v>-7.946518794041017</v>
+        <v>-6.969172918846298</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.6827779472262104</v>
       </c>
       <c r="E91">
-        <v>-24.2584441057027</v>
+        <v>-25.04643481082941</v>
       </c>
       <c r="F91">
-        <v>6.767565115151585</v>
+        <v>6.184553872794946</v>
       </c>
       <c r="G91">
-        <v>-7.287372624444427</v>
+        <v>-6.698433194099161</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4145160578188474</v>
       </c>
       <c r="E92">
-        <v>-26.48677031065705</v>
+        <v>-26.51001043926442</v>
       </c>
       <c r="F92">
-        <v>6.97478511565726</v>
+        <v>5.623153881360394</v>
       </c>
       <c r="G92">
-        <v>-7.903766408946868</v>
+        <v>-5.478351498874001</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.1621759298896452</v>
       </c>
       <c r="E93">
-        <v>-28.16523561617805</v>
+        <v>-28.20123698453903</v>
       </c>
       <c r="F93">
-        <v>6.636804852537412</v>
+        <v>5.757146487747979</v>
       </c>
       <c r="G93">
-        <v>-7.107557032933373</v>
+        <v>-5.011342771285633</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.06776502235477606</v>
       </c>
       <c r="E94">
-        <v>-29.94106990557497</v>
+        <v>-30.20111073275443</v>
       </c>
       <c r="F94">
-        <v>6.464667105470552</v>
+        <v>5.490132086698972</v>
       </c>
       <c r="G94">
-        <v>-5.637274237486714</v>
+        <v>-5.072750080493574</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.2753413607077417</v>
       </c>
       <c r="E95">
-        <v>-31.91992021320976</v>
+        <v>-32.20883006218811</v>
       </c>
       <c r="F95">
-        <v>6.250095542105408</v>
+        <v>5.079123976406381</v>
       </c>
       <c r="G95">
-        <v>-6.127824254404841</v>
+        <v>-4.573847557179866</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.4577628659752958</v>
       </c>
       <c r="E96">
-        <v>-34.8186802022887</v>
+        <v>-34.08868113530422</v>
       </c>
       <c r="F96">
-        <v>5.906406019160401</v>
+        <v>4.550052173823694</v>
       </c>
       <c r="G96">
-        <v>-5.777174581430775</v>
+        <v>-5.053572090184576</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.6159314385598605</v>
       </c>
       <c r="E97">
-        <v>-36.80183708870478</v>
+        <v>-36.71482472488439</v>
       </c>
       <c r="F97">
-        <v>5.645029611170359</v>
+        <v>4.882334263059791</v>
       </c>
       <c r="G97">
-        <v>-5.657342764545777</v>
+        <v>-4.774135562305774</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.7477386539387108</v>
       </c>
       <c r="E98">
-        <v>-38.23815809632463</v>
+        <v>-38.45552937716681</v>
       </c>
       <c r="F98">
-        <v>5.270975694708631</v>
+        <v>4.182936472977507</v>
       </c>
       <c r="G98">
-        <v>-5.484274064843757</v>
+        <v>-4.221529369254009</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.8554504792346436</v>
       </c>
       <c r="E99">
-        <v>-40.12290444984303</v>
+        <v>-41.32992617608448</v>
       </c>
       <c r="F99">
-        <v>5.156953619914737</v>
+        <v>4.017013187922831</v>
       </c>
       <c r="G99">
-        <v>-4.747383043802923</v>
+        <v>-4.034443819738716</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.9328320827875254</v>
       </c>
       <c r="E100">
-        <v>-42.77056961214466</v>
+        <v>-42.33863017587103</v>
       </c>
       <c r="F100">
-        <v>4.798427939953894</v>
+        <v>3.809254727405907</v>
       </c>
       <c r="G100">
-        <v>-4.910179120696584</v>
+        <v>-5.112390552780807</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.9896944276445021</v>
       </c>
       <c r="E101">
-        <v>-45.52867519854535</v>
+        <v>-45.23370398710773</v>
       </c>
       <c r="F101">
-        <v>4.512062236324132</v>
+        <v>3.899845873180874</v>
       </c>
       <c r="G101">
-        <v>-4.46481805038951</v>
+        <v>-3.416239166826293</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.007254458316337</v>
       </c>
       <c r="E102">
-        <v>-46.72162922028198</v>
+        <v>-48.6455876302328</v>
       </c>
       <c r="F102">
-        <v>4.227462364790086</v>
+        <v>2.838322639591953</v>
       </c>
       <c r="G102">
-        <v>-4.741722010930769</v>
+        <v>-3.660938140361523</v>
       </c>
     </row>
   </sheetData>
